--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T18:22:17+00:00</t>
+    <t>2025-11-28T16:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T16:27:44+00:00</t>
+    <t>2025-12-09T10:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R222-MediaTypeCorpsCDANonStructure/FHIR/TRE-R222-MediaTypeCorpsCDANonStructure|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R222-MediaTypeCorpsCDANonStructure/FHIR/TRE-R222-MediaTypeCorpsCDANonStructure|20251222120000</t>
   </si>
   <si>
     <t/>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T10:41:43+00:00</t>
+    <t>2025-12-09T13:35:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T13:35:37+00:00</t>
+    <t>2025-12-09T14:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T14:49:30+00:00</t>
+    <t>2025-12-10T08:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV-MediaTypeCorpsCDANonStructure?vs</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-MediaType-cisis</t>
   </si>
   <si>
     <t>Target</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T08:51:21+00:00</t>
+    <t>2025-12-10T14:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T14:21:49+00:00</t>
+    <t>2025-12-15T13:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T13:43:12+00:00</t>
+    <t>2025-12-16T11:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T11:22:18+00:00</t>
+    <t>2025-12-16T14:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:14:47+00:00</t>
+    <t>2025-12-16T15:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T15:47:53+00:00</t>
+    <t>2025-12-16T16:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T16:52:49+00:00</t>
+    <t>2025-12-17T15:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T15:53:11+00:00</t>
+    <t>2025-12-18T13:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
